--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/112.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/112.xlsx
@@ -426,13 +426,13 @@
         <v>-7.933792249525933</v>
       </c>
       <c r="E2">
-        <v>-29.40668053758882</v>
+        <v>-29.56136868121683</v>
       </c>
       <c r="F2">
-        <v>-4.424243347840041</v>
+        <v>-4.517296343298717</v>
       </c>
       <c r="G2">
-        <v>-18.31014353345576</v>
+        <v>-18.22167251446428</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.144195711995092</v>
       </c>
       <c r="E3">
-        <v>-29.47470274565803</v>
+        <v>-29.84356959595282</v>
       </c>
       <c r="F3">
-        <v>-4.240701982401754</v>
+        <v>-4.316756050387582</v>
       </c>
       <c r="G3">
-        <v>-17.94188672403109</v>
+        <v>-18.32212274248962</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.318542782026739</v>
       </c>
       <c r="E4">
-        <v>-30.2937270831593</v>
+        <v>-30.05249753700771</v>
       </c>
       <c r="F4">
-        <v>-4.202310466751608</v>
+        <v>-4.266623255170156</v>
       </c>
       <c r="G4">
-        <v>-18.0265290971064</v>
+        <v>-17.75928861899428</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.416065900389885</v>
       </c>
       <c r="E5">
-        <v>-30.13676564557944</v>
+        <v>-30.5520199193718</v>
       </c>
       <c r="F5">
-        <v>-4.349074804607805</v>
+        <v>-4.225688651593416</v>
       </c>
       <c r="G5">
-        <v>-17.92446994394898</v>
+        <v>-18.13659645992332</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.418612398588618</v>
       </c>
       <c r="E6">
-        <v>-30.17715057677984</v>
+        <v>-30.19422745226277</v>
       </c>
       <c r="F6">
-        <v>-4.335860687798347</v>
+        <v>-4.133590763750167</v>
       </c>
       <c r="G6">
-        <v>-18.12384092796051</v>
+        <v>-18.0641435155236</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.306894680247771</v>
       </c>
       <c r="E7">
-        <v>-30.66376001551107</v>
+        <v>-30.78807115549563</v>
       </c>
       <c r="F7">
-        <v>-4.232525996136123</v>
+        <v>-4.164000131106937</v>
       </c>
       <c r="G7">
-        <v>-17.96093725833682</v>
+        <v>-18.28132192399087</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.072020970215862</v>
       </c>
       <c r="E8">
-        <v>-31.07036490394878</v>
+        <v>-31.31788223626002</v>
       </c>
       <c r="F8">
-        <v>-4.365961074113873</v>
+        <v>-4.190661964333441</v>
       </c>
       <c r="G8">
-        <v>-17.74860714381182</v>
+        <v>-17.74910207036994</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.700858122664128</v>
       </c>
       <c r="E9">
-        <v>-31.61835101514296</v>
+        <v>-31.48976046722115</v>
       </c>
       <c r="F9">
-        <v>-4.083460453634949</v>
+        <v>-4.0239704202355</v>
       </c>
       <c r="G9">
-        <v>-18.01791505761322</v>
+        <v>-17.91403344913643</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.190486968527241</v>
       </c>
       <c r="E10">
-        <v>-31.79113494090562</v>
+        <v>-32.09364379732902</v>
       </c>
       <c r="F10">
-        <v>-4.29644199656873</v>
+        <v>-4.218159620269371</v>
       </c>
       <c r="G10">
-        <v>-17.80331556412104</v>
+        <v>-18.09378614028224</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.553024327513472</v>
       </c>
       <c r="E11">
-        <v>-32.35192304811949</v>
+        <v>-32.28744437096127</v>
       </c>
       <c r="F11">
-        <v>-4.125389926462452</v>
+        <v>-4.108172309995264</v>
       </c>
       <c r="G11">
-        <v>-17.25008864378067</v>
+        <v>-17.29754365881335</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.805915461803822</v>
       </c>
       <c r="E12">
-        <v>-33.0659456588049</v>
+        <v>-33.3012768675615</v>
       </c>
       <c r="F12">
-        <v>-3.977430254444015</v>
+        <v>-3.943366130106094</v>
       </c>
       <c r="G12">
-        <v>-17.198631179191</v>
+        <v>-17.53460354851671</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.971894109967822</v>
       </c>
       <c r="E13">
-        <v>-33.3500938173642</v>
+        <v>-33.41833112794878</v>
       </c>
       <c r="F13">
-        <v>-4.0157447319257</v>
+        <v>-3.812429408215187</v>
       </c>
       <c r="G13">
-        <v>-17.21781082477277</v>
+        <v>-17.40053969635839</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.092993642350491</v>
       </c>
       <c r="E14">
-        <v>-34.14395568904185</v>
+        <v>-34.1918126023549</v>
       </c>
       <c r="F14">
-        <v>-3.78579656784778</v>
+        <v>-3.779108329437577</v>
       </c>
       <c r="G14">
-        <v>-16.66461204406948</v>
+        <v>-17.07494919784383</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.207573991129508</v>
       </c>
       <c r="E15">
-        <v>-35.02802023447828</v>
+        <v>-34.23988235394632</v>
       </c>
       <c r="F15">
-        <v>-3.774121557672724</v>
+        <v>-3.80263313530968</v>
       </c>
       <c r="G15">
-        <v>-16.31846140248328</v>
+        <v>-16.70689929751536</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.348782806830999</v>
       </c>
       <c r="E16">
-        <v>-35.15727646807921</v>
+        <v>-35.09033656529783</v>
       </c>
       <c r="F16">
-        <v>-3.533767442280837</v>
+        <v>-3.638733189359173</v>
       </c>
       <c r="G16">
-        <v>-16.36583365387748</v>
+        <v>-16.59508893247201</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.555979077508915</v>
       </c>
       <c r="E17">
-        <v>-36.11542911251814</v>
+        <v>-36.08726200419043</v>
       </c>
       <c r="F17">
-        <v>-3.602312359760287</v>
+        <v>-3.327623243889763</v>
       </c>
       <c r="G17">
-        <v>-15.68190308510114</v>
+        <v>-16.45975879664492</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.8557792301903675</v>
       </c>
       <c r="E18">
-        <v>-36.47357253636276</v>
+        <v>-36.38219698783599</v>
       </c>
       <c r="F18">
-        <v>-3.236185564866545</v>
+        <v>-3.143028195115115</v>
       </c>
       <c r="G18">
-        <v>-15.37545250562188</v>
+        <v>-16.00794381780903</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.2626614405988794</v>
       </c>
       <c r="E19">
-        <v>-37.61620389068916</v>
+        <v>-37.031632237987</v>
       </c>
       <c r="F19">
-        <v>-3.160744488758788</v>
+        <v>-3.021522436105081</v>
       </c>
       <c r="G19">
-        <v>-15.29273190423212</v>
+        <v>-15.46200671874613</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.2078250913736464</v>
       </c>
       <c r="E20">
-        <v>-37.64185543170561</v>
+        <v>-38.11043475117529</v>
       </c>
       <c r="F20">
-        <v>-3.15949945255238</v>
+        <v>-3.041756138285862</v>
       </c>
       <c r="G20">
-        <v>-15.0656235144198</v>
+        <v>-15.12913798586349</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.5511427703053107</v>
       </c>
       <c r="E21">
-        <v>-38.18858715559966</v>
+        <v>-38.31004309272239</v>
       </c>
       <c r="F21">
-        <v>-2.815220019540072</v>
+        <v>-2.789735296392946</v>
       </c>
       <c r="G21">
-        <v>-15.11466593603857</v>
+        <v>-15.50172498885354</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.7735556950718958</v>
       </c>
       <c r="E22">
-        <v>-38.38034538745447</v>
+        <v>-38.57977032580425</v>
       </c>
       <c r="F22">
-        <v>-2.636029239701289</v>
+        <v>-2.785344120790705</v>
       </c>
       <c r="G22">
-        <v>-14.51195960206824</v>
+        <v>-15.18729599462464</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.8810735820110104</v>
       </c>
       <c r="E23">
-        <v>-38.51764871936703</v>
+        <v>-39.13140638704862</v>
       </c>
       <c r="F23">
-        <v>-2.605665432551673</v>
+        <v>-2.77322841915736</v>
       </c>
       <c r="G23">
-        <v>-14.30591290297677</v>
+        <v>-14.53899848276024</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.8852147012353461</v>
       </c>
       <c r="E24">
-        <v>-39.27986561467908</v>
+        <v>-39.50226350166978</v>
       </c>
       <c r="F24">
-        <v>-2.659361864335942</v>
+        <v>-2.557122274380219</v>
       </c>
       <c r="G24">
-        <v>-14.54622540367247</v>
+        <v>-14.08015024992618</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.8032090083232064</v>
       </c>
       <c r="E25">
-        <v>-39.69282848062356</v>
+        <v>-39.90106582939227</v>
       </c>
       <c r="F25">
-        <v>-2.469115693139397</v>
+        <v>-2.5965301968336</v>
       </c>
       <c r="G25">
-        <v>-14.36375806518446</v>
+        <v>-14.66367197249642</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.6492560429445607</v>
       </c>
       <c r="E26">
-        <v>-40.02151418104829</v>
+        <v>-39.85909593228919</v>
       </c>
       <c r="F26">
-        <v>-2.136078034150481</v>
+        <v>-2.317352986374708</v>
       </c>
       <c r="G26">
-        <v>-14.33742267541956</v>
+        <v>-14.49070258916058</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.4377152473218274</v>
       </c>
       <c r="E27">
-        <v>-39.96846537228544</v>
+        <v>-39.76069672057651</v>
       </c>
       <c r="F27">
-        <v>-2.325309455278597</v>
+        <v>-2.537762499809392</v>
       </c>
       <c r="G27">
-        <v>-14.12031047786307</v>
+        <v>-14.98871126517869</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.1850162874315288</v>
       </c>
       <c r="E28">
-        <v>-39.93986579468999</v>
+        <v>-40.38108180996833</v>
       </c>
       <c r="F28">
-        <v>-2.491665510578405</v>
+        <v>-2.494419832192714</v>
       </c>
       <c r="G28">
-        <v>-14.27068207734785</v>
+        <v>-14.87705318523015</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.09793723351330366</v>
       </c>
       <c r="E29">
-        <v>-40.11655779352127</v>
+        <v>-40.09780991112952</v>
       </c>
       <c r="F29">
-        <v>-2.412866233019699</v>
+        <v>-2.41653258714449</v>
       </c>
       <c r="G29">
-        <v>-14.3528696809058</v>
+        <v>-14.54554343129138</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.401797324330192</v>
       </c>
       <c r="E30">
-        <v>-39.68235638448082</v>
+        <v>-40.43633824980992</v>
       </c>
       <c r="F30">
-        <v>-2.440174192820388</v>
+        <v>-2.318172241736077</v>
       </c>
       <c r="G30">
-        <v>-14.82216434018903</v>
+        <v>-14.71258528283916</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.7159941737006771</v>
       </c>
       <c r="E31">
-        <v>-39.47383147761262</v>
+        <v>-39.85560447882927</v>
       </c>
       <c r="F31">
-        <v>-2.446163289142628</v>
+        <v>-2.543566041833405</v>
       </c>
       <c r="G31">
-        <v>-14.39456600197292</v>
+        <v>-15.17382041900703</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.036468061084694</v>
       </c>
       <c r="E32">
-        <v>-39.29046450809403</v>
+        <v>-39.41246612633468</v>
       </c>
       <c r="F32">
-        <v>-2.266742223165866</v>
+        <v>-2.6528691206328</v>
       </c>
       <c r="G32">
-        <v>-14.61525193343904</v>
+        <v>-14.93473282016087</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.358375829782074</v>
       </c>
       <c r="E33">
-        <v>-39.45738406001676</v>
+        <v>-39.5918367175415</v>
       </c>
       <c r="F33">
-        <v>-2.49434776422867</v>
+        <v>-2.716006455706776</v>
       </c>
       <c r="G33">
-        <v>-14.83249158699879</v>
+        <v>-14.94095995632024</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.67456284657951</v>
       </c>
       <c r="E34">
-        <v>-38.97917946904378</v>
+        <v>-39.11545710159361</v>
       </c>
       <c r="F34">
-        <v>-2.434798088376219</v>
+        <v>-2.564355578541464</v>
       </c>
       <c r="G34">
-        <v>-14.77070853087214</v>
+        <v>-15.08711723133352</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.984550199990363</v>
       </c>
       <c r="E35">
-        <v>-38.33188845133539</v>
+        <v>-38.78606948769768</v>
       </c>
       <c r="F35">
-        <v>-2.339477022968677</v>
+        <v>-2.389084633252728</v>
       </c>
       <c r="G35">
-        <v>-15.09002223504423</v>
+        <v>-14.87253594584181</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.286060019755352</v>
       </c>
       <c r="E36">
-        <v>-38.06932752837066</v>
+        <v>-38.76467018377443</v>
       </c>
       <c r="F36">
-        <v>-2.501476694097162</v>
+        <v>-2.563219058464824</v>
       </c>
       <c r="G36">
-        <v>-14.67264355090785</v>
+        <v>-14.88140986315983</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.574204046690219</v>
       </c>
       <c r="E37">
-        <v>-37.96847388374584</v>
+        <v>-38.00418995824433</v>
       </c>
       <c r="F37">
-        <v>-2.515539059127087</v>
+        <v>-2.273291295852399</v>
       </c>
       <c r="G37">
-        <v>-15.01631128333959</v>
+        <v>-15.37387668594519</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.848660022348955</v>
       </c>
       <c r="E38">
-        <v>-37.56701787025484</v>
+        <v>-37.34519283522611</v>
       </c>
       <c r="F38">
-        <v>-2.524049705823449</v>
+        <v>-2.455331659556813</v>
       </c>
       <c r="G38">
-        <v>-15.15559255526781</v>
+        <v>-15.38305682872559</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.110019795911593</v>
       </c>
       <c r="E39">
-        <v>-37.08771286009799</v>
+        <v>-36.6715483630301</v>
       </c>
       <c r="F39">
-        <v>-2.464839660606146</v>
+        <v>-2.425752316337648</v>
       </c>
       <c r="G39">
-        <v>-15.08696825678425</v>
+        <v>-15.36744429596239</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.356080743141156</v>
       </c>
       <c r="E40">
-        <v>-36.72494360005454</v>
+        <v>-37.04104693544895</v>
       </c>
       <c r="F40">
-        <v>-2.44383226327115</v>
+        <v>-2.385621229141623</v>
       </c>
       <c r="G40">
-        <v>-15.12915122804565</v>
+        <v>-15.13570445294063</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.587007375954114</v>
       </c>
       <c r="E41">
-        <v>-36.37626468688594</v>
+        <v>-36.46121885926983</v>
       </c>
       <c r="F41">
-        <v>-2.39853299184906</v>
+        <v>-2.4463620973193</v>
       </c>
       <c r="G41">
-        <v>-14.94890857616003</v>
+        <v>-15.09365224822804</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.805593617387859</v>
       </c>
       <c r="E42">
-        <v>-35.51511874840233</v>
+        <v>-35.53978761055911</v>
       </c>
       <c r="F42">
-        <v>-2.426850731513761</v>
+        <v>-2.301691043889978</v>
       </c>
       <c r="G42">
-        <v>-15.35362607888147</v>
+        <v>-15.0750436717518</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.011116594575094</v>
       </c>
       <c r="E43">
-        <v>-35.95331653575455</v>
+        <v>-35.22315217946879</v>
       </c>
       <c r="F43">
-        <v>-2.323924424981116</v>
+        <v>-2.067586132184809</v>
       </c>
       <c r="G43">
-        <v>-14.82655081302856</v>
+        <v>-14.8338538764882</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.202121435279886</v>
       </c>
       <c r="E44">
-        <v>-35.0336423349588</v>
+        <v>-35.07802817294498</v>
       </c>
       <c r="F44">
-        <v>-2.361786613860873</v>
+        <v>-2.255717481402008</v>
       </c>
       <c r="G44">
-        <v>-15.09077703942719</v>
+        <v>-15.28526000294998</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.382141885783366</v>
       </c>
       <c r="E45">
-        <v>-34.82173239376986</v>
+        <v>-34.15497573053951</v>
       </c>
       <c r="F45">
-        <v>-2.237045251775504</v>
+        <v>-2.402907600103243</v>
       </c>
       <c r="G45">
-        <v>-15.18205871158151</v>
+        <v>-15.19226677875185</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.552335819676798</v>
       </c>
       <c r="E46">
-        <v>-33.86416845095194</v>
+        <v>-34.3587163046186</v>
       </c>
       <c r="F46">
-        <v>-2.270713416494887</v>
+        <v>-2.152005054204107</v>
       </c>
       <c r="G46">
-        <v>-14.8721221276494</v>
+        <v>-15.50823352138374</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.710656559331373</v>
       </c>
       <c r="E47">
-        <v>-33.49041537720287</v>
+        <v>-33.8640846741828</v>
       </c>
       <c r="F47">
-        <v>-2.178993264187315</v>
+        <v>-2.226594568621786</v>
       </c>
       <c r="G47">
-        <v>-15.20159258553598</v>
+        <v>-15.43252962126446</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.862517597544074</v>
       </c>
       <c r="E48">
-        <v>-32.6997868359667</v>
+        <v>-33.67913953147254</v>
       </c>
       <c r="F48">
-        <v>-2.149462794644915</v>
+        <v>-2.195370087740661</v>
       </c>
       <c r="G48">
-        <v>-15.0381708155354</v>
+        <v>-15.2653834875322</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.012601723518352</v>
       </c>
       <c r="E49">
-        <v>-32.78249714947979</v>
+        <v>-32.72969514255036</v>
       </c>
       <c r="F49">
-        <v>-2.112773574007522</v>
+        <v>-2.071274023862073</v>
       </c>
       <c r="G49">
-        <v>-15.11460138040055</v>
+        <v>-15.28768001173919</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.159222919933635</v>
       </c>
       <c r="E50">
-        <v>-32.27110563674159</v>
+        <v>-32.01795714700182</v>
       </c>
       <c r="F50">
-        <v>-2.238374781456998</v>
+        <v>-2.242307041518087</v>
       </c>
       <c r="G50">
-        <v>-14.89974035381077</v>
+        <v>-15.19755703052361</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.308966850123</v>
       </c>
       <c r="E51">
-        <v>-31.68361991101551</v>
+        <v>-32.55222198195275</v>
       </c>
       <c r="F51">
-        <v>-2.282126662570659</v>
+        <v>-2.110117828114147</v>
       </c>
       <c r="G51">
-        <v>-15.10421288849832</v>
+        <v>-15.34074805673371</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.46932321338948</v>
       </c>
       <c r="E52">
-        <v>-31.79221724619345</v>
+        <v>-30.90480389422835</v>
       </c>
       <c r="F52">
-        <v>-2.033575023360667</v>
+        <v>-1.87796620674478</v>
       </c>
       <c r="G52">
-        <v>-14.99342879257215</v>
+        <v>-15.34259368587185</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.636959453770602</v>
       </c>
       <c r="E53">
-        <v>-31.14791502133013</v>
+        <v>-31.08203251722954</v>
       </c>
       <c r="F53">
-        <v>-2.127919443600308</v>
+        <v>-2.169604548043985</v>
       </c>
       <c r="G53">
-        <v>-15.03889913555404</v>
+        <v>-15.14095332289315</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.817479992171116</v>
       </c>
       <c r="E54">
-        <v>-30.68354265421357</v>
+        <v>-30.93651906194107</v>
       </c>
       <c r="F54">
-        <v>-2.205849763753478</v>
+        <v>-1.816613175056435</v>
       </c>
       <c r="G54">
-        <v>-15.14902774346343</v>
+        <v>-15.24714734742912</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.018724514270457</v>
       </c>
       <c r="E55">
-        <v>-30.35513319070331</v>
+        <v>-30.28831782095714</v>
       </c>
       <c r="F55">
-        <v>-2.146565993837326</v>
+        <v>-2.126046504902579</v>
       </c>
       <c r="G55">
-        <v>-15.17807115947946</v>
+        <v>-15.50203452486146</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.236093357849837</v>
       </c>
       <c r="E56">
-        <v>-30.03241375478369</v>
+        <v>-30.17977482746729</v>
       </c>
       <c r="F56">
-        <v>-2.162031613247592</v>
+        <v>-2.061828978735353</v>
       </c>
       <c r="G56">
-        <v>-15.41540251391704</v>
+        <v>-15.15910835463051</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.471014019765279</v>
       </c>
       <c r="E57">
-        <v>-29.54024787844505</v>
+        <v>-30.26646566963313</v>
       </c>
       <c r="F57">
-        <v>-2.168947652693565</v>
+        <v>-1.887325101661609</v>
       </c>
       <c r="G57">
-        <v>-15.42156840498393</v>
+        <v>-15.57012748078596</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.728249171540254</v>
       </c>
       <c r="E58">
-        <v>-29.22406982322951</v>
+        <v>-29.50590846004489</v>
       </c>
       <c r="F58">
-        <v>-2.350191955323889</v>
+        <v>-2.075133387591716</v>
       </c>
       <c r="G58">
-        <v>-15.74398077978078</v>
+        <v>-15.91482975869872</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.000335923075389</v>
       </c>
       <c r="E59">
-        <v>-29.02037453389049</v>
+        <v>-29.25377208424582</v>
       </c>
       <c r="F59">
-        <v>-2.267134869314793</v>
+        <v>-2.25016990490546</v>
       </c>
       <c r="G59">
-        <v>-15.76978482698663</v>
+        <v>-15.44971135261328</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.281673130909046</v>
       </c>
       <c r="E60">
-        <v>-28.79621507051081</v>
+        <v>-28.49574629162787</v>
       </c>
       <c r="F60">
-        <v>-2.310276243652592</v>
+        <v>-2.452078660766019</v>
       </c>
       <c r="G60">
-        <v>-15.62218084357269</v>
+        <v>-16.37646878142239</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.573747927200143</v>
       </c>
       <c r="E61">
-        <v>-28.70254358566214</v>
+        <v>-28.57231373014956</v>
       </c>
       <c r="F61">
-        <v>-2.254272808651526</v>
+        <v>-2.196035266765109</v>
       </c>
       <c r="G61">
-        <v>-15.61198436331173</v>
+        <v>-15.87827637012686</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.869228936135467</v>
       </c>
       <c r="E62">
-        <v>-28.16881311064411</v>
+        <v>-28.45045702307716</v>
       </c>
       <c r="F62">
-        <v>-2.45564726753728</v>
+        <v>-2.459508288001728</v>
       </c>
       <c r="G62">
-        <v>-15.61096802583118</v>
+        <v>-15.97990515236418</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.159135945547909</v>
       </c>
       <c r="E63">
-        <v>-28.15503296423877</v>
+        <v>-28.32754518156097</v>
       </c>
       <c r="F63">
-        <v>-2.580337270843675</v>
+        <v>-2.476967787750533</v>
       </c>
       <c r="G63">
-        <v>-15.90558340500754</v>
+        <v>-16.24390957221167</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.443919894313613</v>
       </c>
       <c r="E64">
-        <v>-28.0434694785858</v>
+        <v>-27.62779179247372</v>
       </c>
       <c r="F64">
-        <v>-2.458590456919426</v>
+        <v>-2.398903272078111</v>
       </c>
       <c r="G64">
-        <v>-15.97271133690734</v>
+        <v>-16.09540677568381</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.717454922205025</v>
       </c>
       <c r="E65">
-        <v>-27.91664050705298</v>
+        <v>-28.2077715725321</v>
       </c>
       <c r="F65">
-        <v>-2.535355264136856</v>
+        <v>-2.521495020753215</v>
       </c>
       <c r="G65">
-        <v>-15.79281629230334</v>
+        <v>-16.40836257714773</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.96715203099548</v>
       </c>
       <c r="E66">
-        <v>-27.37934612299091</v>
+        <v>-27.28427986814788</v>
       </c>
       <c r="F66">
-        <v>-2.634855443091522</v>
+        <v>-2.621799544455999</v>
       </c>
       <c r="G66">
-        <v>-16.11484464381764</v>
+        <v>-16.26258767014424</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.190867470581122</v>
       </c>
       <c r="E67">
-        <v>-27.68743179515474</v>
+        <v>-27.90680013303431</v>
       </c>
       <c r="F67">
-        <v>-2.840032108356126</v>
+        <v>-2.619008774675967</v>
       </c>
       <c r="G67">
-        <v>-16.0502261054366</v>
+        <v>-15.96830831134011</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.384081719741086</v>
       </c>
       <c r="E68">
-        <v>-27.66776463253943</v>
+        <v>-27.94224449909235</v>
       </c>
       <c r="F68">
-        <v>-2.758203491205383</v>
+        <v>-2.745805316287682</v>
       </c>
       <c r="G68">
-        <v>-15.94463791073432</v>
+        <v>-16.52185800987057</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.533033776343515</v>
       </c>
       <c r="E69">
-        <v>-27.60721440658287</v>
+        <v>-27.457335502351</v>
       </c>
       <c r="F69">
-        <v>-2.989250898826818</v>
+        <v>-2.932451402751661</v>
       </c>
       <c r="G69">
-        <v>-15.75013673921106</v>
+        <v>-16.65565867365852</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.634776009160397</v>
       </c>
       <c r="E70">
-        <v>-27.47491050997477</v>
+        <v>-28.224834862593</v>
       </c>
       <c r="F70">
-        <v>-3.030614596718208</v>
+        <v>-2.863817021592708</v>
       </c>
       <c r="G70">
-        <v>-15.97978597272476</v>
+        <v>-15.98671328926569</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.68962830407915</v>
       </c>
       <c r="E71">
-        <v>-27.36494557564651</v>
+        <v>-27.08836449715404</v>
       </c>
       <c r="F71">
-        <v>-3.118573132649668</v>
+        <v>-3.09984623077458</v>
       </c>
       <c r="G71">
-        <v>-15.62011506315618</v>
+        <v>-16.0813700625973</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.687182142229963</v>
       </c>
       <c r="E72">
-        <v>-27.23013743291218</v>
+        <v>-27.28845059270894</v>
       </c>
       <c r="F72">
-        <v>-3.178801241405012</v>
+        <v>-3.196224292988094</v>
       </c>
       <c r="G72">
-        <v>-15.73022380779234</v>
+        <v>-15.92894095905987</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.62652958822971</v>
       </c>
       <c r="E73">
-        <v>-27.1513374567047</v>
+        <v>-27.35206206709469</v>
       </c>
       <c r="F73">
-        <v>-3.160481896292101</v>
+        <v>-3.010978975802249</v>
       </c>
       <c r="G73">
-        <v>-15.62975537176654</v>
+        <v>-16.19636186190388</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.516285015031055</v>
       </c>
       <c r="E74">
-        <v>-27.97756659635218</v>
+        <v>-27.70258859765842</v>
       </c>
       <c r="F74">
-        <v>-3.32603360684379</v>
+        <v>-3.386252603557703</v>
       </c>
       <c r="G74">
-        <v>-15.51322085823866</v>
+        <v>-16.16964410412919</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.353393939086766</v>
       </c>
       <c r="E75">
-        <v>-27.6646173431041</v>
+        <v>-27.95510083680012</v>
       </c>
       <c r="F75">
-        <v>-3.303386042051252</v>
+        <v>-3.360755454899534</v>
       </c>
       <c r="G75">
-        <v>-15.20832126934455</v>
+        <v>-15.96108635624619</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.141230182718305</v>
       </c>
       <c r="E76">
-        <v>-27.71584344107887</v>
+        <v>-27.88549366282822</v>
       </c>
       <c r="F76">
-        <v>-3.498960272382604</v>
+        <v>-3.509018309387395</v>
       </c>
       <c r="G76">
-        <v>-15.51365288443153</v>
+        <v>-15.55536079240804</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.893908476149655</v>
       </c>
       <c r="E77">
-        <v>-27.68815182252196</v>
+        <v>-28.4124042559907</v>
       </c>
       <c r="F77">
-        <v>-3.502439415474362</v>
+        <v>-3.373189249615555</v>
       </c>
       <c r="G77">
-        <v>-15.57724018787708</v>
+        <v>-15.90919521019088</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.614279440707797</v>
       </c>
       <c r="E78">
-        <v>-28.23495600200014</v>
+        <v>-28.57873057781843</v>
       </c>
       <c r="F78">
-        <v>-3.680402554822197</v>
+        <v>-3.49211795763548</v>
       </c>
       <c r="G78">
-        <v>-15.01276568906703</v>
+        <v>-15.42642497529004</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.305641462456441</v>
       </c>
       <c r="E79">
-        <v>-28.71285492097761</v>
+        <v>-28.82460407406489</v>
       </c>
       <c r="F79">
-        <v>-3.607211324580443</v>
+        <v>-3.612607309842279</v>
       </c>
       <c r="G79">
-        <v>-14.5637332237569</v>
+        <v>-15.35794634081022</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.982444916047157</v>
       </c>
       <c r="E80">
-        <v>-29.12346977314911</v>
+        <v>-28.60422135800761</v>
       </c>
       <c r="F80">
-        <v>-3.664186434544993</v>
+        <v>-3.706220281665249</v>
       </c>
       <c r="G80">
-        <v>-14.91103262464523</v>
+        <v>-15.21200590652976</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.650614930057013</v>
       </c>
       <c r="E81">
-        <v>-29.20075723903802</v>
+        <v>-29.33343247051475</v>
       </c>
       <c r="F81">
-        <v>-3.759501701380715</v>
+        <v>-3.731514480309731</v>
       </c>
       <c r="G81">
-        <v>-14.64191837775787</v>
+        <v>-15.0806749097141</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.312555045892636</v>
       </c>
       <c r="E82">
-        <v>-29.52398386404651</v>
+        <v>-30.34184664796481</v>
       </c>
       <c r="F82">
-        <v>-3.63259250180222</v>
+        <v>-3.847178592395224</v>
       </c>
       <c r="G82">
-        <v>-14.44528521490732</v>
+        <v>-15.04044847086642</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.981771000276469</v>
       </c>
       <c r="E83">
-        <v>-30.66455929117342</v>
+        <v>-30.34072358641091</v>
       </c>
       <c r="F83">
-        <v>-3.716391805004224</v>
+        <v>-3.781903241054623</v>
       </c>
       <c r="G83">
-        <v>-14.12102058988125</v>
+        <v>-14.47305407089073</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.667166525790432</v>
       </c>
       <c r="E84">
-        <v>-30.8669911362643</v>
+        <v>-30.76612390621745</v>
       </c>
       <c r="F84">
-        <v>-3.932617234687367</v>
+        <v>-3.730710963929016</v>
       </c>
       <c r="G84">
-        <v>-14.04456685119732</v>
+        <v>-14.61857572116047</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.371403062776109</v>
       </c>
       <c r="E85">
-        <v>-31.18020983371583</v>
+        <v>-31.66236778249752</v>
       </c>
       <c r="F85">
-        <v>-3.929162114250291</v>
+        <v>-3.829046458315345</v>
       </c>
       <c r="G85">
-        <v>-14.24320620464467</v>
+        <v>-14.3761792320478</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.10726316482771</v>
       </c>
       <c r="E86">
-        <v>-32.04096858767179</v>
+        <v>-32.16950932237951</v>
       </c>
       <c r="F86">
-        <v>-4.131087437458906</v>
+        <v>-3.998480726883956</v>
       </c>
       <c r="G86">
-        <v>-13.98755925701107</v>
+        <v>-14.60106127998496</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.886054525248896</v>
       </c>
       <c r="E87">
-        <v>-33.03602603103622</v>
+        <v>-33.33028174358063</v>
       </c>
       <c r="F87">
-        <v>-4.07001522232011</v>
+        <v>-4.078748699847825</v>
       </c>
       <c r="G87">
-        <v>-13.77123331402016</v>
+        <v>-14.33056488033496</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.708622631764246</v>
       </c>
       <c r="E88">
-        <v>-33.37865943140458</v>
+        <v>-33.95995246892517</v>
       </c>
       <c r="F88">
-        <v>-4.20780005752996</v>
+        <v>-4.089765157937656</v>
       </c>
       <c r="G88">
-        <v>-13.87231089042519</v>
+        <v>-14.37127631410414</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.5825927669375</v>
       </c>
       <c r="E89">
-        <v>-34.72454454885425</v>
+        <v>-34.65395922449669</v>
       </c>
       <c r="F89">
-        <v>-4.302305181045745</v>
+        <v>-4.199140304701094</v>
       </c>
       <c r="G89">
-        <v>-14.26906984167022</v>
+        <v>-13.99093932400666</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.515870018566722</v>
       </c>
       <c r="E90">
-        <v>-35.31420620634102</v>
+        <v>-35.43458210241291</v>
       </c>
       <c r="F90">
-        <v>-4.217052093051828</v>
+        <v>-4.234474316267507</v>
       </c>
       <c r="G90">
-        <v>-14.03479081021985</v>
+        <v>-14.51052944639528</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.501422465165815</v>
       </c>
       <c r="E91">
-        <v>-36.56143851753359</v>
+        <v>-36.63297255719576</v>
       </c>
       <c r="F91">
-        <v>-4.552459711180154</v>
+        <v>-4.280519118352118</v>
       </c>
       <c r="G91">
-        <v>-13.90435862651811</v>
+        <v>-14.33708168922901</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.536798425294414</v>
       </c>
       <c r="E92">
-        <v>-37.81447180392998</v>
+        <v>-38.72354484707378</v>
       </c>
       <c r="F92">
-        <v>-4.521496994398314</v>
+        <v>-4.391241190512508</v>
       </c>
       <c r="G92">
-        <v>-14.08722985156191</v>
+        <v>-14.62643826681624</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.623378910852034</v>
       </c>
       <c r="E93">
-        <v>-38.68788311426338</v>
+        <v>-39.42812785369021</v>
       </c>
       <c r="F93">
-        <v>-4.471054389772241</v>
+        <v>-4.435577070645143</v>
       </c>
       <c r="G93">
-        <v>-14.27865221573365</v>
+        <v>-14.66670112166486</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.746996974764197</v>
       </c>
       <c r="E94">
-        <v>-39.93344441854712</v>
+        <v>-40.65822215500075</v>
       </c>
       <c r="F94">
-        <v>-4.399011276750768</v>
+        <v>-4.500376939096538</v>
       </c>
       <c r="G94">
-        <v>-14.39172058808191</v>
+        <v>-14.64839049428715</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.899617300491643</v>
       </c>
       <c r="E95">
-        <v>-41.36722268801166</v>
+        <v>-41.59591288963601</v>
       </c>
       <c r="F95">
-        <v>-4.777588433708586</v>
+        <v>-4.690422645381606</v>
       </c>
       <c r="G95">
-        <v>-14.11364634969252</v>
+        <v>-15.04521234589743</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.077519062268523</v>
       </c>
       <c r="E96">
-        <v>-42.42766903180985</v>
+        <v>-43.93733094022092</v>
       </c>
       <c r="F96">
-        <v>-4.850281815141257</v>
+        <v>-4.996433161119382</v>
       </c>
       <c r="G96">
-        <v>-14.81091014062828</v>
+        <v>-14.6891962786042</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.263642933311822</v>
       </c>
       <c r="E97">
-        <v>-44.60109654636921</v>
+        <v>-44.823544246574</v>
       </c>
       <c r="F97">
-        <v>-4.972675584007092</v>
+        <v>-5.048544097694694</v>
       </c>
       <c r="G97">
-        <v>-14.7778626197825</v>
+        <v>-15.0942431806068</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.443831324108643</v>
       </c>
       <c r="E98">
-        <v>-45.93946666120316</v>
+        <v>-46.37626288585</v>
       </c>
       <c r="F98">
-        <v>-4.962600979654245</v>
+        <v>-5.056922205606607</v>
       </c>
       <c r="G98">
-        <v>-15.14570064519646</v>
+        <v>-15.42844606334177</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.610744033824068</v>
       </c>
       <c r="E99">
-        <v>-47.6742865615126</v>
+        <v>-47.64962449206683</v>
       </c>
       <c r="F99">
-        <v>-5.064616082043809</v>
+        <v>-4.992806568629926</v>
       </c>
       <c r="G99">
-        <v>-15.15561572908658</v>
+        <v>-15.65405477602479</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.747715329608879</v>
       </c>
       <c r="E100">
-        <v>-49.13057813950628</v>
+        <v>-49.69739817409836</v>
       </c>
       <c r="F100">
-        <v>-5.162148060049423</v>
+        <v>-5.354789869774865</v>
       </c>
       <c r="G100">
-        <v>-15.34901614421804</v>
+        <v>-16.65859678282462</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.840532086444855</v>
       </c>
       <c r="E101">
-        <v>-50.83923817759192</v>
+        <v>-50.61763164143406</v>
       </c>
       <c r="F101">
-        <v>-5.363087626048708</v>
+        <v>-5.248371994639421</v>
       </c>
       <c r="G101">
-        <v>-15.99965752232424</v>
+        <v>-16.1133201375968</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.882677729261362</v>
       </c>
       <c r="E102">
-        <v>-52.56247763774525</v>
+        <v>-52.78241203487578</v>
       </c>
       <c r="F102">
-        <v>-5.426675592989806</v>
+        <v>-5.44946977881264</v>
       </c>
       <c r="G102">
-        <v>-15.64315480483674</v>
+        <v>-16.32225859821683</v>
       </c>
     </row>
   </sheetData>
